--- a/data/Anomaly_north.xlsx
+++ b/data/Anomaly_north.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HONOURS\DavinaG_2025_Honours\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A6002E-F69D-479C-9A21-3F8D01B92F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D86B52-D057-4B8D-BAC0-D5AE4AA5DB1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="2610" windowWidth="19420" windowHeight="11500" xr2:uid="{BEB1D32C-34AC-4FC8-857C-21BA495B982F}"/>
   </bookViews>
